--- a/eventos-pdf.xlsx
+++ b/eventos-pdf.xlsx
@@ -11493,12 +11493,16 @@
       <c r="J181" s="14" t="s">
         <v>706</v>
       </c>
-      <c r="K181" s="16"/>
+      <c r="K181" s="16" t="n">
+        <v>12</v>
+      </c>
       <c r="L181" s="16"/>
       <c r="M181" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="N181" s="16"/>
+      <c r="N181" s="16" t="n">
+        <v>12</v>
+      </c>
       <c r="O181" s="13" t="s">
         <v>187</v>
       </c>
@@ -15183,7 +15187,7 @@
       </c>
       <c r="G59" s="24" t="n">
         <f aca="false">SUMIF(Eventos!$A$2:$A$209,$A59,Eventos!$K$2:$K$209)</f>
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="H59" s="24" t="n">
         <f aca="false">SUMIF(Eventos!$A$2:$A$209,$A59,Eventos!$L$2:$L$209)</f>
@@ -15195,7 +15199,7 @@
       </c>
       <c r="J59" s="24" t="n">
         <f aca="false">SUMIF(Eventos!$A$2:$A$209,$A59,Eventos!$N$2:$N$209)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K59" s="23" t="n">
         <f aca="false">COUNTIFS(Eventos!$A$2:$A$209,$A59,Eventos!$Q$2:$Q$209,"&lt;&gt;")</f>
@@ -15586,7 +15590,7 @@
       </c>
       <c r="G69" s="26" t="n">
         <f aca="false">SUM(G2:G68)</f>
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="H69" s="26" t="n">
         <f aca="false">SUM(H2:H68)</f>
@@ -15598,7 +15602,7 @@
       </c>
       <c r="J69" s="26" t="n">
         <f aca="false">SUM(J2:J68)</f>
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="K69" s="25" t="n">
         <f aca="false">SUM(K2:K68)</f>

--- a/eventos-pdf.xlsx
+++ b/eventos-pdf.xlsx
@@ -2290,7 +2290,7 @@
     <t xml:space="preserve">-fama -politica +conocimiento</t>
   </si>
   <si>
-    <t xml:space="preserve">Accedés a hacer las pasadas.</t>
+    <t xml:space="preserve">Accedes pero sin muchas ganas</t>
   </si>
   <si>
     <t xml:space="preserve">A la tercera pasada te confiesa que le chupa un huevo. Pela un porro y van a la plaza seca a escuchar a Los Redondos. Te revela que en realidad era Duki Green Son.</t>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="K134" s="16"/>
       <c r="L134" s="16" t="n">
-        <v>22</v>
+        <v>-22</v>
       </c>
       <c r="M134" s="16"/>
       <c r="N134" s="16"/>
@@ -14631,7 +14631,7 @@
       </c>
       <c r="H45" s="24" t="n">
         <f aca="false">SUMIF(Eventos!$A$2:$A$209,$A45,Eventos!$L$2:$L$209)</f>
-        <v>32</v>
+        <v>-12</v>
       </c>
       <c r="I45" s="24" t="n">
         <f aca="false">SUMIF(Eventos!$A$2:$A$209,$A45,Eventos!$M$2:$M$209)</f>
@@ -15594,7 +15594,7 @@
       </c>
       <c r="H69" s="26" t="n">
         <f aca="false">SUM(H2:H68)</f>
-        <v>40</v>
+        <v>-4</v>
       </c>
       <c r="I69" s="26" t="n">
         <f aca="false">SUM(I2:I68)</f>

--- a/eventos-pdf.xlsx
+++ b/eventos-pdf.xlsx
@@ -11493,9 +11493,7 @@
       <c r="J181" s="14" t="s">
         <v>706</v>
       </c>
-      <c r="K181" s="16" t="n">
-        <v>12</v>
-      </c>
+      <c r="K181" s="16"/>
       <c r="L181" s="16"/>
       <c r="M181" s="16" t="n">
         <v>12</v>
@@ -15187,7 +15185,7 @@
       </c>
       <c r="G59" s="24" t="n">
         <f aca="false">SUMIF(Eventos!$A$2:$A$209,$A59,Eventos!$K$2:$K$209)</f>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="H59" s="24" t="n">
         <f aca="false">SUMIF(Eventos!$A$2:$A$209,$A59,Eventos!$L$2:$L$209)</f>
@@ -15590,7 +15588,7 @@
       </c>
       <c r="G69" s="26" t="n">
         <f aca="false">SUM(G2:G68)</f>
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="H69" s="26" t="n">
         <f aca="false">SUM(H2:H68)</f>
